--- a/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:AT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,157 @@
         </is>
       </c>
       <c r="AT2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11:51:33</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>240331</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32803</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2222</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2131</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>3394</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3210</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>9145</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12187</v>
+      </c>
+      <c r="R3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2222</v>
+      </c>
+      <c r="T3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3816</v>
+      </c>
+      <c r="V3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT3"/>
+  <dimension ref="A1:AT4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,157 @@
         </is>
       </c>
       <c r="AT3" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>12:00:07</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E4" t="n">
+        <v>240245</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32838</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="I4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2227</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3432</v>
+      </c>
+      <c r="N4" t="n">
+        <v>38</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>9120</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12229</v>
+      </c>
+      <c r="R4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2227</v>
+      </c>
+      <c r="T4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V4" t="n">
+        <v>35</v>
+      </c>
+      <c r="W4" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT4"/>
+  <dimension ref="A1:AT5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,6 +1099,157 @@
         </is>
       </c>
       <c r="AT4" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:01:18</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E5" t="n">
+        <v>240247</v>
+      </c>
+      <c r="F5" t="n">
+        <v>32836</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="I5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2225</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3434</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>9118</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12234</v>
+      </c>
+      <c r="R5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2225</v>
+      </c>
+      <c r="T5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V5" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT5"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,6 +1250,157 @@
         </is>
       </c>
       <c r="AT5" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12:02:31</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>240321</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32844</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="I6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2224</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>3436</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>9118</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12235</v>
+      </c>
+      <c r="R6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2224</v>
+      </c>
+      <c r="T6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V6" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_SILVERM_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT6"/>
+  <dimension ref="A1:AT7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1401,6 +1401,157 @@
         </is>
       </c>
       <c r="AT6" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12:03:42</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>240325</v>
+      </c>
+      <c r="F7" t="n">
+        <v>32842</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="I7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2225</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>3433</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>9117</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12222</v>
+      </c>
+      <c r="R7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2225</v>
+      </c>
+      <c r="T7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3823</v>
+      </c>
+      <c r="V7" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.08799999999999999</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
